--- a/uploads/2026-07-24T16-39-58-978Z-input-template.xlsx
+++ b/uploads/2026-07-24T16-39-58-978Z-input-template.xlsx
@@ -404,7 +404,7 @@
         <v>query</v>
       </c>
       <c r="B1" t="str">
-        <v>reference_answer</v>
+        <v>response</v>
       </c>
     </row>
     <row r="2">
